--- a/input_data.xlsx
+++ b/input_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/weigu/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/weigu/Documents/Exercise/qzz_autoType/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27893338-69ED-9049-815F-0BDA0414E7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008AEB46-5CF3-C249-B310-23A6AB6DF7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="2180" windowWidth="28100" windowHeight="17360" xr2:uid="{8B1B3161-B270-384F-BA23-5AA6E4650D06}"/>
+    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="20460" xr2:uid="{8B1B3161-B270-384F-BA23-5AA6E4650D06}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="204">
   <si>
     <t>企业名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -99,10 +99,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>成立时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -720,6 +716,32 @@
   </si>
   <si>
     <t>secondCode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>福建省 xxxxx 有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xxxxx华亭镇华林工业园</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>说明：
+1、省市区及所属行业请按顺序选择，不要手动输入，code 列请勿修改
+2、标红列均为必填项
+3、第一列为示例，请勿修改，从第四行开始录入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莆田市鑫龙鞋业有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>制造业</t>
+  </si>
+  <si>
+    <t>tCMtsj5+SRbxdub540itVw==</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -730,7 +752,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -746,21 +768,59 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -769,12 +829,30 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1110,116 +1188,173 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA2E47FE-C844-5240-8BE9-FEA7EB7E19A5}">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="32.6640625" customWidth="1"/>
     <col min="3" max="4" width="13.33203125" customWidth="1"/>
+    <col min="9" max="9" width="45.1640625" customWidth="1"/>
     <col min="10" max="10" width="34.1640625" customWidth="1"/>
     <col min="11" max="11" width="17.1640625" customWidth="1"/>
     <col min="12" max="12" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:13" ht="67" customHeight="1">
+      <c r="A1" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="5">
+        <f>VLOOKUP(C3,sheet2!A:B,2,FALSE)</f>
+        <v>350000</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="5">
+        <f>VLOOKUP(E3,sheet2!C:D,2,FALSE)</f>
+        <v>350300</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H3" s="5">
+        <f>VLOOKUP(G3,sheet2!E:F,2,FALSE)</f>
+        <v>350322</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K3" s="5">
+        <f>VLOOKUP(J3,Sheet3!A:B,2,FALSE)</f>
+        <v>10057</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="M3" s="5">
+        <f>VLOOKUP(L3,Sheet3!C:D,2,FALSE)</f>
+        <v>359</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="L1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" t="s">
-        <v>198</v>
-      </c>
-      <c r="N1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4">
+        <f>VLOOKUP(C3,sheet2!A:B,2,FALSE)</f>
+        <v>350000</v>
+      </c>
+      <c r="E4" t="s">
         <v>12</v>
       </c>
-      <c r="D2">
-        <f>VLOOKUP(C2,sheet2!A:B,2,FALSE)</f>
-        <v>350000</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2">
-        <f>VLOOKUP(E2,sheet2!C:D,2,FALSE)</f>
+      <c r="F4">
+        <f>VLOOKUP(E3,sheet2!C:D,2,FALSE)</f>
         <v>350300</v>
       </c>
-      <c r="G2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H2">
-        <f>VLOOKUP(G2,sheet2!E:F,2,FALSE)</f>
-        <v>350322</v>
-      </c>
-      <c r="J2" t="s">
-        <v>87</v>
-      </c>
-      <c r="K2">
-        <f>VLOOKUP(J2,Sheet3!A:B,2,FALSE)</f>
-        <v>10057</v>
-      </c>
-      <c r="L2" t="s">
-        <v>91</v>
-      </c>
-      <c r="M2">
-        <f>VLOOKUP(L2,Sheet3!C:D,2,FALSE)</f>
-        <v>359</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3">
-        <v>2</v>
+      <c r="G4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4">
+        <f>VLOOKUP(G4,sheet2!E:F,2,FALSE)</f>
+        <v>350304</v>
+      </c>
+      <c r="I4" t="s">
+        <v>203</v>
+      </c>
+      <c r="J4" t="s">
+        <v>202</v>
+      </c>
+      <c r="L4" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{107AFD8A-FE7D-E141-B82C-3FDF47235C83}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C1048576" xr:uid="{107AFD8A-FE7D-E141-B82C-3FDF47235C83}">
       <formula1>省</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576 G2:G1048576 L2:L1048576" xr:uid="{1B598FD6-123C-7E4F-8E23-947CF644E04E}">
-      <formula1>INDIRECT(C2)</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J1048576" xr:uid="{EF5F83EB-8102-6549-BB35-721D92BBA3D8}">
+      <formula1>行业_一级</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576" xr:uid="{EF5F83EB-8102-6549-BB35-721D92BBA3D8}">
-      <formula1>行业_一级</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G1048576 L3:L1048576 E3:E1048576" xr:uid="{1B598FD6-123C-7E4F-8E23-947CF644E04E}">
+      <formula1>INDIRECT(C3)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1233,30 +1368,30 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
         <v>8</v>
-      </c>
-      <c r="E1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B2">
         <v>350000</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D2">
         <v>350300</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2">
         <v>350303</v>
@@ -1264,19 +1399,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B3">
         <v>440000</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D3">
         <v>442000</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F3">
         <v>350305</v>
@@ -1284,19 +1419,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B4">
         <v>320000</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4">
         <v>441200</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F4">
         <v>350322</v>
@@ -1304,19 +1439,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B5">
         <v>460000</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D5">
         <v>320100</v>
       </c>
       <c r="E5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F5">
         <v>350302</v>
@@ -1324,19 +1459,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>350000</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D6">
         <v>320200</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6">
         <v>350304</v>
@@ -1344,13 +1479,13 @@
     </row>
     <row r="7" spans="1:6">
       <c r="C7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D7">
         <v>320700</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F7">
         <v>442000</v>
@@ -1358,13 +1493,13 @@
     </row>
     <row r="8" spans="1:6">
       <c r="C8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D8">
         <v>460100</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F8">
         <v>441225</v>
@@ -1372,13 +1507,13 @@
     </row>
     <row r="9" spans="1:6">
       <c r="C9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D9">
         <v>350500</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F9">
         <v>441226</v>
@@ -1386,7 +1521,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="E10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F10">
         <v>441204</v>
@@ -1394,7 +1529,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="E11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F11">
         <v>441224</v>
@@ -1402,7 +1537,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="E12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F12">
         <v>441223</v>
@@ -1410,7 +1545,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="E13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F13">
         <v>441203</v>
@@ -1418,7 +1553,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="E14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F14">
         <v>441284</v>
@@ -1426,7 +1561,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="E15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F15">
         <v>441202</v>
@@ -1434,7 +1569,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="E16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F16">
         <v>320115</v>
@@ -1442,7 +1577,7 @@
     </row>
     <row r="17" spans="5:6">
       <c r="E17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F17">
         <v>320106</v>
@@ -1450,7 +1585,7 @@
     </row>
     <row r="18" spans="5:6">
       <c r="E18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F18">
         <v>320105</v>
@@ -1458,7 +1593,7 @@
     </row>
     <row r="19" spans="5:6">
       <c r="E19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F19">
         <v>320116</v>
@@ -1466,7 +1601,7 @@
     </row>
     <row r="20" spans="5:6">
       <c r="E20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F20">
         <v>320111</v>
@@ -1474,7 +1609,7 @@
     </row>
     <row r="21" spans="5:6">
       <c r="E21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F21">
         <v>320117</v>
@@ -1482,7 +1617,7 @@
     </row>
     <row r="22" spans="5:6">
       <c r="E22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F22">
         <v>320118</v>
@@ -1490,7 +1625,7 @@
     </row>
     <row r="23" spans="5:6">
       <c r="E23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F23">
         <v>320113</v>
@@ -1498,7 +1633,7 @@
     </row>
     <row r="24" spans="5:6">
       <c r="E24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F24">
         <v>320102</v>
@@ -1506,7 +1641,7 @@
     </row>
     <row r="25" spans="5:6">
       <c r="E25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F25">
         <v>320104</v>
@@ -1514,7 +1649,7 @@
     </row>
     <row r="26" spans="5:6">
       <c r="E26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F26">
         <v>320114</v>
@@ -1522,7 +1657,7 @@
     </row>
     <row r="27" spans="5:6">
       <c r="E27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F27">
         <v>320281</v>
@@ -1530,7 +1665,7 @@
     </row>
     <row r="28" spans="5:6">
       <c r="E28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F28">
         <v>320211</v>
@@ -1538,7 +1673,7 @@
     </row>
     <row r="29" spans="5:6">
       <c r="E29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F29">
         <v>320206</v>
@@ -1546,7 +1681,7 @@
     </row>
     <row r="30" spans="5:6">
       <c r="E30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F30">
         <v>320213</v>
@@ -1554,7 +1689,7 @@
     </row>
     <row r="31" spans="5:6">
       <c r="E31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F31">
         <v>320205</v>
@@ -1562,7 +1697,7 @@
     </row>
     <row r="32" spans="5:6">
       <c r="E32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F32">
         <v>320282</v>
@@ -1570,7 +1705,7 @@
     </row>
     <row r="33" spans="5:6">
       <c r="E33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F33">
         <v>320214</v>
@@ -1578,7 +1713,7 @@
     </row>
     <row r="34" spans="5:6">
       <c r="E34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F34">
         <v>320723</v>
@@ -1586,7 +1721,7 @@
     </row>
     <row r="35" spans="5:6">
       <c r="E35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F35">
         <v>320724</v>
@@ -1594,7 +1729,7 @@
     </row>
     <row r="36" spans="5:6">
       <c r="E36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F36">
         <v>320707</v>
@@ -1602,7 +1737,7 @@
     </row>
     <row r="37" spans="5:6">
       <c r="E37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F37">
         <v>320722</v>
@@ -1610,7 +1745,7 @@
     </row>
     <row r="38" spans="5:6">
       <c r="E38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F38">
         <v>320703</v>
@@ -1618,7 +1753,7 @@
     </row>
     <row r="39" spans="5:6">
       <c r="E39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F39">
         <v>320706</v>
@@ -1626,7 +1761,7 @@
     </row>
     <row r="40" spans="5:6">
       <c r="E40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F40">
         <v>460108</v>
@@ -1634,7 +1769,7 @@
     </row>
     <row r="41" spans="5:6">
       <c r="E41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F41">
         <v>460106</v>
@@ -1642,7 +1777,7 @@
     </row>
     <row r="42" spans="5:6">
       <c r="E42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F42">
         <v>460107</v>
@@ -1650,7 +1785,7 @@
     </row>
     <row r="43" spans="5:6">
       <c r="E43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F43">
         <v>460105</v>
@@ -1658,7 +1793,7 @@
     </row>
     <row r="44" spans="5:6">
       <c r="E44" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F44">
         <v>350524</v>
@@ -1666,7 +1801,7 @@
     </row>
     <row r="45" spans="5:6">
       <c r="E45" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F45">
         <v>350526</v>
@@ -1674,7 +1809,7 @@
     </row>
     <row r="46" spans="5:6">
       <c r="E46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F46">
         <v>350582</v>
@@ -1682,7 +1817,7 @@
     </row>
     <row r="47" spans="5:6">
       <c r="E47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F47">
         <v>350581</v>
@@ -1690,7 +1825,7 @@
     </row>
     <row r="48" spans="5:6">
       <c r="E48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F48">
         <v>350504</v>
@@ -1698,7 +1833,7 @@
     </row>
     <row r="49" spans="5:6">
       <c r="E49" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F49">
         <v>350502</v>
@@ -1706,7 +1841,7 @@
     </row>
     <row r="50" spans="5:6">
       <c r="E50" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F50">
         <v>350503</v>
@@ -1714,7 +1849,7 @@
     </row>
     <row r="51" spans="5:6">
       <c r="E51" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F51">
         <v>350525</v>
@@ -1722,7 +1857,7 @@
     </row>
     <row r="52" spans="5:6">
       <c r="E52" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F52">
         <v>350521</v>
@@ -1730,7 +1865,7 @@
     </row>
     <row r="53" spans="5:6">
       <c r="E53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F53">
         <v>350505</v>
@@ -1738,7 +1873,7 @@
     </row>
     <row r="54" spans="5:6">
       <c r="E54" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F54">
         <v>350583</v>
@@ -1746,7 +1881,7 @@
     </row>
     <row r="55" spans="5:6">
       <c r="E55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F55">
         <v>350527</v>
@@ -1770,27 +1905,27 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" t="s">
         <v>83</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>85</v>
-      </c>
-      <c r="C1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B2">
         <v>10057</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D2">
         <v>359</v>
@@ -1798,13 +1933,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B3">
         <v>10058</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D3">
         <v>360</v>
@@ -1812,13 +1947,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B4">
         <v>10059</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D4">
         <v>361</v>
@@ -1826,13 +1961,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B5">
         <v>10060</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D5">
         <v>362</v>
@@ -1840,13 +1975,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B6">
         <v>10061</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6">
         <v>363</v>
@@ -1854,13 +1989,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B7">
         <v>10062</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7">
         <v>364</v>
@@ -1868,13 +2003,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B8">
         <v>10063</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D8">
         <v>365</v>
@@ -1882,13 +2017,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B9">
         <v>10064</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D9">
         <v>366</v>
@@ -1896,13 +2031,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B10">
         <v>10065</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D10">
         <v>367</v>
@@ -1910,13 +2045,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B11">
         <v>10066</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D11">
         <v>368</v>
@@ -1924,13 +2059,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B12">
         <v>10067</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>369</v>
@@ -1938,13 +2073,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B13">
         <v>10068</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D13">
         <v>370</v>
@@ -1952,13 +2087,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B14">
         <v>10069</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D14">
         <v>371</v>
@@ -1966,13 +2101,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B15">
         <v>10071</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D15">
         <v>372</v>
@@ -1980,13 +2115,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B16">
         <v>10073</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D16">
         <v>373</v>
@@ -1994,13 +2129,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B17">
         <v>10056</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D17">
         <v>374</v>
@@ -2008,13 +2143,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B18">
         <v>10055</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D18">
         <v>375</v>
@@ -2022,13 +2157,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B19">
         <v>10054</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D19">
         <v>376</v>
@@ -2036,7 +2171,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="C20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D20">
         <v>377</v>
@@ -2044,7 +2179,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="C21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D21">
         <v>378</v>
@@ -2052,7 +2187,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="C22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D22">
         <v>379</v>
@@ -2060,7 +2195,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="C23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D23">
         <v>380</v>
@@ -2068,7 +2203,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="C24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D24">
         <v>381</v>
@@ -2076,7 +2211,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="C25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D25">
         <v>382</v>
@@ -2084,7 +2219,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="C26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D26">
         <v>383</v>
@@ -2092,7 +2227,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="C27" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D27">
         <v>384</v>
@@ -2100,7 +2235,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="C28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D28">
         <v>385</v>
@@ -2108,7 +2243,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="C29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D29">
         <v>386</v>
@@ -2116,7 +2251,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="C30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D30">
         <v>387</v>
@@ -2124,7 +2259,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="C31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D31">
         <v>388</v>
@@ -2132,7 +2267,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="C32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D32">
         <v>389</v>
@@ -2140,7 +2275,7 @@
     </row>
     <row r="33" spans="3:4">
       <c r="C33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D33">
         <v>390</v>
@@ -2148,7 +2283,7 @@
     </row>
     <row r="34" spans="3:4">
       <c r="C34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D34">
         <v>391</v>
@@ -2156,7 +2291,7 @@
     </row>
     <row r="35" spans="3:4">
       <c r="C35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D35">
         <v>392</v>
@@ -2164,7 +2299,7 @@
     </row>
     <row r="36" spans="3:4">
       <c r="C36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D36">
         <v>393</v>
@@ -2172,7 +2307,7 @@
     </row>
     <row r="37" spans="3:4">
       <c r="C37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D37">
         <v>394</v>
@@ -2180,7 +2315,7 @@
     </row>
     <row r="38" spans="3:4">
       <c r="C38" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D38">
         <v>395</v>
@@ -2188,7 +2323,7 @@
     </row>
     <row r="39" spans="3:4">
       <c r="C39" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D39">
         <v>396</v>
@@ -2196,7 +2331,7 @@
     </row>
     <row r="40" spans="3:4">
       <c r="C40" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D40">
         <v>398</v>
@@ -2204,7 +2339,7 @@
     </row>
     <row r="41" spans="3:4">
       <c r="C41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D41">
         <v>399</v>
@@ -2212,7 +2347,7 @@
     </row>
     <row r="42" spans="3:4">
       <c r="C42" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D42">
         <v>405</v>
@@ -2220,7 +2355,7 @@
     </row>
     <row r="43" spans="3:4">
       <c r="C43" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D43">
         <v>406</v>
@@ -2228,7 +2363,7 @@
     </row>
     <row r="44" spans="3:4">
       <c r="C44" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D44">
         <v>407</v>
@@ -2236,7 +2371,7 @@
     </row>
     <row r="45" spans="3:4">
       <c r="C45" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D45">
         <v>408</v>
@@ -2244,7 +2379,7 @@
     </row>
     <row r="46" spans="3:4">
       <c r="C46" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D46">
         <v>409</v>
@@ -2252,7 +2387,7 @@
     </row>
     <row r="47" spans="3:4">
       <c r="C47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D47">
         <v>410</v>
@@ -2260,7 +2395,7 @@
     </row>
     <row r="48" spans="3:4">
       <c r="C48" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D48">
         <v>397</v>
@@ -2268,7 +2403,7 @@
     </row>
     <row r="49" spans="3:4">
       <c r="C49" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D49">
         <v>328</v>
@@ -2276,7 +2411,7 @@
     </row>
     <row r="50" spans="3:4">
       <c r="C50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D50">
         <v>329</v>
@@ -2284,7 +2419,7 @@
     </row>
     <row r="51" spans="3:4">
       <c r="C51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D51">
         <v>330</v>
@@ -2292,7 +2427,7 @@
     </row>
     <row r="52" spans="3:4">
       <c r="C52" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D52">
         <v>331</v>
@@ -2300,7 +2435,7 @@
     </row>
     <row r="53" spans="3:4">
       <c r="C53" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D53">
         <v>332</v>
@@ -2308,7 +2443,7 @@
     </row>
     <row r="54" spans="3:4">
       <c r="C54" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D54">
         <v>333</v>
@@ -2316,7 +2451,7 @@
     </row>
     <row r="55" spans="3:4">
       <c r="C55" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D55">
         <v>334</v>
@@ -2324,7 +2459,7 @@
     </row>
     <row r="56" spans="3:4">
       <c r="C56" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D56">
         <v>335</v>
@@ -2332,7 +2467,7 @@
     </row>
     <row r="57" spans="3:4">
       <c r="C57" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D57">
         <v>336</v>
@@ -2340,7 +2475,7 @@
     </row>
     <row r="58" spans="3:4">
       <c r="C58" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D58">
         <v>337</v>
@@ -2348,7 +2483,7 @@
     </row>
     <row r="59" spans="3:4">
       <c r="C59" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D59">
         <v>338</v>
@@ -2356,7 +2491,7 @@
     </row>
     <row r="60" spans="3:4">
       <c r="C60" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D60">
         <v>339</v>
@@ -2364,7 +2499,7 @@
     </row>
     <row r="61" spans="3:4">
       <c r="C61" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D61">
         <v>340</v>
@@ -2372,7 +2507,7 @@
     </row>
     <row r="62" spans="3:4">
       <c r="C62" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D62">
         <v>341</v>
@@ -2380,7 +2515,7 @@
     </row>
     <row r="63" spans="3:4">
       <c r="C63" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D63">
         <v>342</v>
@@ -2388,7 +2523,7 @@
     </row>
     <row r="64" spans="3:4">
       <c r="C64" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D64">
         <v>343</v>
@@ -2396,7 +2531,7 @@
     </row>
     <row r="65" spans="3:4">
       <c r="C65" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D65">
         <v>344</v>
@@ -2404,7 +2539,7 @@
     </row>
     <row r="66" spans="3:4">
       <c r="C66" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D66">
         <v>345</v>
@@ -2412,7 +2547,7 @@
     </row>
     <row r="67" spans="3:4">
       <c r="C67" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D67">
         <v>346</v>
@@ -2420,7 +2555,7 @@
     </row>
     <row r="68" spans="3:4">
       <c r="C68" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D68">
         <v>347</v>
@@ -2428,7 +2563,7 @@
     </row>
     <row r="69" spans="3:4">
       <c r="C69" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D69">
         <v>348</v>
@@ -2436,7 +2571,7 @@
     </row>
     <row r="70" spans="3:4">
       <c r="C70" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D70">
         <v>349</v>
@@ -2444,7 +2579,7 @@
     </row>
     <row r="71" spans="3:4">
       <c r="C71" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D71">
         <v>350</v>
@@ -2452,7 +2587,7 @@
     </row>
     <row r="72" spans="3:4">
       <c r="C72" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D72">
         <v>351</v>
@@ -2460,7 +2595,7 @@
     </row>
     <row r="73" spans="3:4">
       <c r="C73" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D73">
         <v>352</v>
@@ -2468,7 +2603,7 @@
     </row>
     <row r="74" spans="3:4">
       <c r="C74" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D74">
         <v>353</v>
@@ -2476,7 +2611,7 @@
     </row>
     <row r="75" spans="3:4">
       <c r="C75" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D75">
         <v>354</v>
@@ -2484,7 +2619,7 @@
     </row>
     <row r="76" spans="3:4">
       <c r="C76" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D76">
         <v>355</v>
@@ -2492,7 +2627,7 @@
     </row>
     <row r="77" spans="3:4">
       <c r="C77" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D77">
         <v>356</v>
@@ -2500,7 +2635,7 @@
     </row>
     <row r="78" spans="3:4">
       <c r="C78" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D78">
         <v>357</v>
@@ -2508,7 +2643,7 @@
     </row>
     <row r="79" spans="3:4">
       <c r="C79" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D79">
         <v>358</v>
@@ -2516,7 +2651,7 @@
     </row>
     <row r="80" spans="3:4">
       <c r="C80" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D80">
         <v>321</v>
@@ -2524,7 +2659,7 @@
     </row>
     <row r="81" spans="3:4">
       <c r="C81" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D81">
         <v>322</v>
@@ -2532,7 +2667,7 @@
     </row>
     <row r="82" spans="3:4">
       <c r="C82" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D82">
         <v>323</v>
@@ -2540,7 +2675,7 @@
     </row>
     <row r="83" spans="3:4">
       <c r="C83" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D83">
         <v>324</v>
@@ -2548,7 +2683,7 @@
     </row>
     <row r="84" spans="3:4">
       <c r="C84" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D84">
         <v>325</v>
@@ -2556,7 +2691,7 @@
     </row>
     <row r="85" spans="3:4">
       <c r="C85" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D85">
         <v>326</v>
@@ -2564,7 +2699,7 @@
     </row>
     <row r="86" spans="3:4">
       <c r="C86" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D86">
         <v>327</v>
@@ -2572,7 +2707,7 @@
     </row>
     <row r="87" spans="3:4">
       <c r="C87" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D87">
         <v>316</v>
@@ -2580,7 +2715,7 @@
     </row>
     <row r="88" spans="3:4">
       <c r="C88" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D88">
         <v>317</v>
@@ -2588,7 +2723,7 @@
     </row>
     <row r="89" spans="3:4">
       <c r="C89" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D89">
         <v>318</v>
@@ -2596,7 +2731,7 @@
     </row>
     <row r="90" spans="3:4">
       <c r="C90" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D90">
         <v>319</v>
@@ -2604,7 +2739,7 @@
     </row>
     <row r="91" spans="3:4">
       <c r="C91" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D91">
         <v>320</v>

--- a/input_data.xlsx
+++ b/input_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/weigu/Documents/Exercise/qzz_autoType/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008AEB46-5CF3-C249-B310-23A6AB6DF7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6443785-B437-E442-A136-0445CB90F1CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="20460" xr2:uid="{8B1B3161-B270-384F-BA23-5AA6E4650D06}"/>
+    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="20460" activeTab="2" xr2:uid="{8B1B3161-B270-384F-BA23-5AA6E4650D06}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="294">
   <si>
     <t>企业名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -738,11 +738,281 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>制造业</t>
-  </si>
-  <si>
     <t>tCMtsj5+SRbxdub540itVw==</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>506638468429029376</t>
+  </si>
+  <si>
+    <t>506638468429029377</t>
+  </si>
+  <si>
+    <t>506638468429029378</t>
+  </si>
+  <si>
+    <t>506638468429029379</t>
+  </si>
+  <si>
+    <t>506638468429029380</t>
+  </si>
+  <si>
+    <t>506638468429029381</t>
+  </si>
+  <si>
+    <t>506638468433223680</t>
+  </si>
+  <si>
+    <t>506638468433223681</t>
+  </si>
+  <si>
+    <t>506638468433223682</t>
+  </si>
+  <si>
+    <t>506638468433223683</t>
+  </si>
+  <si>
+    <t>506638468433223684</t>
+  </si>
+  <si>
+    <t>506638468437417984</t>
+  </si>
+  <si>
+    <t>506638468437417985</t>
+  </si>
+  <si>
+    <t>506638468437417986</t>
+  </si>
+  <si>
+    <t>506638468437417987</t>
+  </si>
+  <si>
+    <t>506638468437417988</t>
+  </si>
+  <si>
+    <t>506638468437417989</t>
+  </si>
+  <si>
+    <t>506638468437417990</t>
+  </si>
+  <si>
+    <t>506638468437417991</t>
+  </si>
+  <si>
+    <t>506638468437417992</t>
+  </si>
+  <si>
+    <t>506638468437417993</t>
+  </si>
+  <si>
+    <t>506638468437417994</t>
+  </si>
+  <si>
+    <t>506638468437417995</t>
+  </si>
+  <si>
+    <t>506638468437417996</t>
+  </si>
+  <si>
+    <t>506638468437417997</t>
+  </si>
+  <si>
+    <t>506638468437417998</t>
+  </si>
+  <si>
+    <t>506638468437417999</t>
+  </si>
+  <si>
+    <t>506638468437418000</t>
+  </si>
+  <si>
+    <t>506638468441612288</t>
+  </si>
+  <si>
+    <t>506638468441612289</t>
+  </si>
+  <si>
+    <t>506638468441612290</t>
+  </si>
+  <si>
+    <t>506638468441612291</t>
+  </si>
+  <si>
+    <t>506638468441612292</t>
+  </si>
+  <si>
+    <t>506638468441612293</t>
+  </si>
+  <si>
+    <t>506638468441612294</t>
+  </si>
+  <si>
+    <t>506638468441612295</t>
+  </si>
+  <si>
+    <t>506638468441612296</t>
+  </si>
+  <si>
+    <t>506638468441612297</t>
+  </si>
+  <si>
+    <t>506638468441612298</t>
+  </si>
+  <si>
+    <t>506638468441612299</t>
+  </si>
+  <si>
+    <t>506638468441612300</t>
+  </si>
+  <si>
+    <t>506638468441612301</t>
+  </si>
+  <si>
+    <t>506638468441612302</t>
+  </si>
+  <si>
+    <t>506638468441612303</t>
+  </si>
+  <si>
+    <t>506638468441612304</t>
+  </si>
+  <si>
+    <t>506638468441612305</t>
+  </si>
+  <si>
+    <t>506638468441612306</t>
+  </si>
+  <si>
+    <t>506638468441612307</t>
+  </si>
+  <si>
+    <t>506638468441612308</t>
+  </si>
+  <si>
+    <t>506638468441612309</t>
+  </si>
+  <si>
+    <t>506638468441612310</t>
+  </si>
+  <si>
+    <t>506638468441612311</t>
+  </si>
+  <si>
+    <t>506638468441612312</t>
+  </si>
+  <si>
+    <t>506638468441612313</t>
+  </si>
+  <si>
+    <t>506638468441612314</t>
+  </si>
+  <si>
+    <t>506638468441612315</t>
+  </si>
+  <si>
+    <t>506638468441612316</t>
+  </si>
+  <si>
+    <t>506638468441612317</t>
+  </si>
+  <si>
+    <t>506638468441612318</t>
+  </si>
+  <si>
+    <t>506638468441612319</t>
+  </si>
+  <si>
+    <t>506638468441612320</t>
+  </si>
+  <si>
+    <t>506638468441612321</t>
+  </si>
+  <si>
+    <t>506638468441612322</t>
+  </si>
+  <si>
+    <t>506638468441612323</t>
+  </si>
+  <si>
+    <t>506638468445806592</t>
+  </si>
+  <si>
+    <t>506638468445806593</t>
+  </si>
+  <si>
+    <t>506638468445806594</t>
+  </si>
+  <si>
+    <t>506638468445806595</t>
+  </si>
+  <si>
+    <t>506638468445806596</t>
+  </si>
+  <si>
+    <t>506638468445806597</t>
+  </si>
+  <si>
+    <t>506638468445806598</t>
+  </si>
+  <si>
+    <t>506638468445806599</t>
+  </si>
+  <si>
+    <t>506638468445806600</t>
+  </si>
+  <si>
+    <t>506638468445806601</t>
+  </si>
+  <si>
+    <t>506638468445806602</t>
+  </si>
+  <si>
+    <t>506638468445806603</t>
+  </si>
+  <si>
+    <t>506638468445806604</t>
+  </si>
+  <si>
+    <t>506638468445806605</t>
+  </si>
+  <si>
+    <t>506638468445806606</t>
+  </si>
+  <si>
+    <t>506638468445806607</t>
+  </si>
+  <si>
+    <t>506638468445806608</t>
+  </si>
+  <si>
+    <t>506638468445806609</t>
+  </si>
+  <si>
+    <t>506638468445806610</t>
+  </si>
+  <si>
+    <t>506638468445806611</t>
+  </si>
+  <si>
+    <t>506638468445806612</t>
+  </si>
+  <si>
+    <t>506638468445806613</t>
+  </si>
+  <si>
+    <t>506638468445806614</t>
+  </si>
+  <si>
+    <t>506638468445806615</t>
+  </si>
+  <si>
+    <t>506638468445806616</t>
+  </si>
+  <si>
+    <t>506638468445806617</t>
+  </si>
+  <si>
+    <t>批发和零售业</t>
   </si>
 </sst>
 </file>
@@ -829,7 +1099,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -846,6 +1116,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1200,21 +1473,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="67" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
@@ -1293,14 +1566,14 @@
       </c>
       <c r="K3" s="5">
         <f>VLOOKUP(J3,Sheet3!A:B,2,FALSE)</f>
-        <v>10057</v>
+        <v>100086</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="5" t="str">
         <f>VLOOKUP(L3,Sheet3!C:D,2,FALSE)</f>
-        <v>359</v>
+        <v>506638468429029376</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1332,13 +1605,21 @@
         <v>350304</v>
       </c>
       <c r="I4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J4" t="s">
-        <v>202</v>
+        <v>293</v>
+      </c>
+      <c r="K4" s="5">
+        <f>VLOOKUP(J4,Sheet3!A:B,2,FALSE)</f>
+        <v>100088</v>
       </c>
       <c r="L4" t="s">
         <v>140</v>
+      </c>
+      <c r="M4" s="5" t="str">
+        <f>VLOOKUP(L4,Sheet3!C:D,2,FALSE)</f>
+        <v>506638468441612312</v>
       </c>
     </row>
   </sheetData>
@@ -1900,7 +2181,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="32.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
+    <col min="3" max="4" width="32.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1922,13 +2203,13 @@
         <v>178</v>
       </c>
       <c r="B2">
-        <v>10057</v>
+        <v>100086</v>
       </c>
       <c r="C2" t="s">
         <v>90</v>
       </c>
-      <c r="D2">
-        <v>359</v>
+      <c r="D2" s="6" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1936,13 +2217,13 @@
         <v>179</v>
       </c>
       <c r="B3">
-        <v>10058</v>
+        <v>100087</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
       </c>
-      <c r="D3">
-        <v>360</v>
+      <c r="D3" s="6" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1950,13 +2231,13 @@
         <v>180</v>
       </c>
       <c r="B4">
-        <v>10059</v>
+        <v>100088</v>
       </c>
       <c r="C4" t="s">
         <v>92</v>
       </c>
-      <c r="D4">
-        <v>361</v>
+      <c r="D4" s="6" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1964,13 +2245,13 @@
         <v>181</v>
       </c>
       <c r="B5">
-        <v>10060</v>
+        <v>100089</v>
       </c>
       <c r="C5" t="s">
         <v>93</v>
       </c>
-      <c r="D5">
-        <v>362</v>
+      <c r="D5" s="6" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1978,13 +2259,13 @@
         <v>87</v>
       </c>
       <c r="B6">
-        <v>10061</v>
+        <v>100090</v>
       </c>
       <c r="C6" t="s">
         <v>94</v>
       </c>
-      <c r="D6">
-        <v>363</v>
+      <c r="D6" s="6" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1992,13 +2273,13 @@
         <v>182</v>
       </c>
       <c r="B7">
-        <v>10062</v>
+        <v>100091</v>
       </c>
       <c r="C7" t="s">
         <v>95</v>
       </c>
-      <c r="D7">
-        <v>364</v>
+      <c r="D7" s="6" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2006,13 +2287,13 @@
         <v>183</v>
       </c>
       <c r="B8">
-        <v>10063</v>
+        <v>100092</v>
       </c>
       <c r="C8" t="s">
         <v>96</v>
       </c>
-      <c r="D8">
-        <v>365</v>
+      <c r="D8" s="6" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2020,13 +2301,13 @@
         <v>184</v>
       </c>
       <c r="B9">
-        <v>10064</v>
+        <v>100093</v>
       </c>
       <c r="C9" t="s">
         <v>97</v>
       </c>
-      <c r="D9">
-        <v>366</v>
+      <c r="D9" s="6" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2034,13 +2315,13 @@
         <v>185</v>
       </c>
       <c r="B10">
-        <v>10065</v>
+        <v>100094</v>
       </c>
       <c r="C10" t="s">
         <v>98</v>
       </c>
-      <c r="D10">
-        <v>367</v>
+      <c r="D10" s="6" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2048,13 +2329,13 @@
         <v>186</v>
       </c>
       <c r="B11">
-        <v>10066</v>
+        <v>100095</v>
       </c>
       <c r="C11" t="s">
         <v>99</v>
       </c>
-      <c r="D11">
-        <v>368</v>
+      <c r="D11" s="6" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2062,13 +2343,13 @@
         <v>187</v>
       </c>
       <c r="B12">
-        <v>10067</v>
+        <v>100096</v>
       </c>
       <c r="C12" t="s">
         <v>100</v>
       </c>
-      <c r="D12">
-        <v>369</v>
+      <c r="D12" s="6" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2076,13 +2357,13 @@
         <v>188</v>
       </c>
       <c r="B13">
-        <v>10068</v>
+        <v>100097</v>
       </c>
       <c r="C13" t="s">
         <v>101</v>
       </c>
-      <c r="D13">
-        <v>370</v>
+      <c r="D13" s="6" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2090,13 +2371,13 @@
         <v>189</v>
       </c>
       <c r="B14">
-        <v>10069</v>
+        <v>100098</v>
       </c>
       <c r="C14" t="s">
         <v>102</v>
       </c>
-      <c r="D14">
-        <v>371</v>
+      <c r="D14" s="6" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2104,13 +2385,13 @@
         <v>190</v>
       </c>
       <c r="B15">
-        <v>10071</v>
+        <v>100099</v>
       </c>
       <c r="C15" t="s">
         <v>103</v>
       </c>
-      <c r="D15">
-        <v>372</v>
+      <c r="D15" s="6" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2118,13 +2399,13 @@
         <v>191</v>
       </c>
       <c r="B16">
-        <v>10073</v>
+        <v>100100</v>
       </c>
       <c r="C16" t="s">
         <v>104</v>
       </c>
-      <c r="D16">
-        <v>373</v>
+      <c r="D16" s="6" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2132,13 +2413,13 @@
         <v>192</v>
       </c>
       <c r="B17">
-        <v>10056</v>
+        <v>100101</v>
       </c>
       <c r="C17" t="s">
         <v>105</v>
       </c>
-      <c r="D17">
-        <v>374</v>
+      <c r="D17" s="6" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2146,13 +2427,13 @@
         <v>193</v>
       </c>
       <c r="B18">
-        <v>10055</v>
+        <v>100102</v>
       </c>
       <c r="C18" t="s">
         <v>106</v>
       </c>
-      <c r="D18">
-        <v>375</v>
+      <c r="D18" s="6" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2160,589 +2441,589 @@
         <v>194</v>
       </c>
       <c r="B19">
-        <v>10054</v>
+        <v>100103</v>
       </c>
       <c r="C19" t="s">
         <v>107</v>
       </c>
-      <c r="D19">
-        <v>376</v>
+      <c r="D19" s="6" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="C20" t="s">
         <v>108</v>
       </c>
-      <c r="D20">
-        <v>377</v>
+      <c r="D20" s="6" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="C21" t="s">
         <v>109</v>
       </c>
-      <c r="D21">
-        <v>378</v>
+      <c r="D21" s="6" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="C22" t="s">
         <v>110</v>
       </c>
-      <c r="D22">
-        <v>379</v>
+      <c r="D22" s="6" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="C23" t="s">
         <v>111</v>
       </c>
-      <c r="D23">
-        <v>380</v>
+      <c r="D23" s="6" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="C24" t="s">
         <v>112</v>
       </c>
-      <c r="D24">
-        <v>381</v>
+      <c r="D24" s="6" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="C25" t="s">
         <v>113</v>
       </c>
-      <c r="D25">
-        <v>382</v>
+      <c r="D25" s="6" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="C26" t="s">
         <v>114</v>
       </c>
-      <c r="D26">
-        <v>383</v>
+      <c r="D26" s="6" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="C27" t="s">
         <v>115</v>
       </c>
-      <c r="D27">
-        <v>384</v>
+      <c r="D27" s="6" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="C28" t="s">
         <v>88</v>
       </c>
-      <c r="D28">
-        <v>385</v>
+      <c r="D28" s="6" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="C29" t="s">
         <v>116</v>
       </c>
-      <c r="D29">
-        <v>386</v>
+      <c r="D29" s="6" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="C30" t="s">
         <v>117</v>
       </c>
-      <c r="D30">
-        <v>387</v>
+      <c r="D30" s="6" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="C31" t="s">
         <v>118</v>
       </c>
-      <c r="D31">
-        <v>388</v>
+      <c r="D31" s="6" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="C32" t="s">
         <v>119</v>
       </c>
-      <c r="D32">
-        <v>389</v>
+      <c r="D32" s="6" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="33" spans="3:4">
       <c r="C33" t="s">
         <v>120</v>
       </c>
-      <c r="D33">
-        <v>390</v>
+      <c r="D33" s="6" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="34" spans="3:4">
       <c r="C34" t="s">
         <v>121</v>
       </c>
-      <c r="D34">
-        <v>391</v>
+      <c r="D34" s="6" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="35" spans="3:4">
       <c r="C35" t="s">
         <v>122</v>
       </c>
-      <c r="D35">
-        <v>392</v>
+      <c r="D35" s="6" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="36" spans="3:4">
       <c r="C36" t="s">
         <v>123</v>
       </c>
-      <c r="D36">
-        <v>393</v>
+      <c r="D36" s="6" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="37" spans="3:4">
       <c r="C37" t="s">
         <v>124</v>
       </c>
-      <c r="D37">
-        <v>394</v>
+      <c r="D37" s="6" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="38" spans="3:4">
       <c r="C38" t="s">
         <v>125</v>
       </c>
-      <c r="D38">
-        <v>395</v>
+      <c r="D38" s="6" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="39" spans="3:4">
       <c r="C39" t="s">
         <v>126</v>
       </c>
-      <c r="D39">
-        <v>396</v>
+      <c r="D39" s="6" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="40" spans="3:4">
       <c r="C40" t="s">
         <v>127</v>
       </c>
-      <c r="D40">
-        <v>398</v>
+      <c r="D40" s="6" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="41" spans="3:4">
       <c r="C41" t="s">
         <v>128</v>
       </c>
-      <c r="D41">
-        <v>399</v>
+      <c r="D41" s="6" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="42" spans="3:4">
       <c r="C42" t="s">
         <v>129</v>
       </c>
-      <c r="D42">
-        <v>405</v>
+      <c r="D42" s="6" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="43" spans="3:4">
       <c r="C43" t="s">
         <v>130</v>
       </c>
-      <c r="D43">
-        <v>406</v>
+      <c r="D43" s="6" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="44" spans="3:4">
       <c r="C44" t="s">
         <v>131</v>
       </c>
-      <c r="D44">
-        <v>407</v>
+      <c r="D44" s="6" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="45" spans="3:4">
       <c r="C45" t="s">
         <v>132</v>
       </c>
-      <c r="D45">
-        <v>408</v>
+      <c r="D45" s="6" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="46" spans="3:4">
       <c r="C46" t="s">
         <v>133</v>
       </c>
-      <c r="D46">
-        <v>409</v>
+      <c r="D46" s="6" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="47" spans="3:4">
       <c r="C47" t="s">
         <v>134</v>
       </c>
-      <c r="D47">
-        <v>410</v>
+      <c r="D47" s="6" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="48" spans="3:4">
       <c r="C48" t="s">
         <v>89</v>
       </c>
-      <c r="D48">
-        <v>397</v>
+      <c r="D48" s="6" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="49" spans="3:4">
       <c r="C49" t="s">
         <v>135</v>
       </c>
-      <c r="D49">
-        <v>328</v>
+      <c r="D49" s="6" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="50" spans="3:4">
       <c r="C50" t="s">
         <v>136</v>
       </c>
-      <c r="D50">
-        <v>329</v>
+      <c r="D50" s="6" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="51" spans="3:4">
       <c r="C51" t="s">
         <v>137</v>
       </c>
-      <c r="D51">
-        <v>330</v>
+      <c r="D51" s="6" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="52" spans="3:4">
       <c r="C52" t="s">
         <v>138</v>
       </c>
-      <c r="D52">
-        <v>331</v>
+      <c r="D52" s="6" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="53" spans="3:4">
       <c r="C53" t="s">
         <v>139</v>
       </c>
-      <c r="D53">
-        <v>332</v>
+      <c r="D53" s="6" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="54" spans="3:4">
       <c r="C54" t="s">
         <v>140</v>
       </c>
-      <c r="D54">
-        <v>333</v>
+      <c r="D54" s="6" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="55" spans="3:4">
       <c r="C55" t="s">
         <v>141</v>
       </c>
-      <c r="D55">
-        <v>334</v>
+      <c r="D55" s="6" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="56" spans="3:4">
       <c r="C56" t="s">
         <v>142</v>
       </c>
-      <c r="D56">
-        <v>335</v>
+      <c r="D56" s="6" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="57" spans="3:4">
       <c r="C57" t="s">
         <v>143</v>
       </c>
-      <c r="D57">
-        <v>336</v>
+      <c r="D57" s="6" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="58" spans="3:4">
       <c r="C58" t="s">
         <v>144</v>
       </c>
-      <c r="D58">
-        <v>337</v>
+      <c r="D58" s="6" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="59" spans="3:4">
       <c r="C59" t="s">
         <v>145</v>
       </c>
-      <c r="D59">
-        <v>338</v>
+      <c r="D59" s="6" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="60" spans="3:4">
       <c r="C60" t="s">
         <v>146</v>
       </c>
-      <c r="D60">
-        <v>339</v>
+      <c r="D60" s="6" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="61" spans="3:4">
       <c r="C61" t="s">
         <v>147</v>
       </c>
-      <c r="D61">
-        <v>340</v>
+      <c r="D61" s="6" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="62" spans="3:4">
       <c r="C62" t="s">
         <v>148</v>
       </c>
-      <c r="D62">
-        <v>341</v>
+      <c r="D62" s="6" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="63" spans="3:4">
       <c r="C63" t="s">
         <v>149</v>
       </c>
-      <c r="D63">
-        <v>342</v>
+      <c r="D63" s="6" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="64" spans="3:4">
       <c r="C64" t="s">
         <v>150</v>
       </c>
-      <c r="D64">
-        <v>343</v>
+      <c r="D64" s="6" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="65" spans="3:4">
       <c r="C65" t="s">
         <v>151</v>
       </c>
-      <c r="D65">
-        <v>344</v>
+      <c r="D65" s="6" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="66" spans="3:4">
       <c r="C66" t="s">
         <v>152</v>
       </c>
-      <c r="D66">
-        <v>345</v>
+      <c r="D66" s="6" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="67" spans="3:4">
       <c r="C67" t="s">
         <v>153</v>
       </c>
-      <c r="D67">
-        <v>346</v>
+      <c r="D67" s="6" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="68" spans="3:4">
       <c r="C68" t="s">
         <v>154</v>
       </c>
-      <c r="D68">
-        <v>347</v>
+      <c r="D68" s="6" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="69" spans="3:4">
       <c r="C69" t="s">
         <v>155</v>
       </c>
-      <c r="D69">
-        <v>348</v>
+      <c r="D69" s="6" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="70" spans="3:4">
       <c r="C70" t="s">
         <v>156</v>
       </c>
-      <c r="D70">
-        <v>349</v>
+      <c r="D70" s="6" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="71" spans="3:4">
       <c r="C71" t="s">
         <v>157</v>
       </c>
-      <c r="D71">
-        <v>350</v>
+      <c r="D71" s="6" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="72" spans="3:4">
       <c r="C72" t="s">
         <v>158</v>
       </c>
-      <c r="D72">
-        <v>351</v>
+      <c r="D72" s="6" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="73" spans="3:4">
       <c r="C73" t="s">
         <v>159</v>
       </c>
-      <c r="D73">
-        <v>352</v>
+      <c r="D73" s="6" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="74" spans="3:4">
       <c r="C74" t="s">
         <v>160</v>
       </c>
-      <c r="D74">
-        <v>353</v>
+      <c r="D74" s="6" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="75" spans="3:4">
       <c r="C75" t="s">
         <v>161</v>
       </c>
-      <c r="D75">
-        <v>354</v>
+      <c r="D75" s="6" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="76" spans="3:4">
       <c r="C76" t="s">
         <v>162</v>
       </c>
-      <c r="D76">
-        <v>355</v>
+      <c r="D76" s="6" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="77" spans="3:4">
       <c r="C77" t="s">
         <v>163</v>
       </c>
-      <c r="D77">
-        <v>356</v>
+      <c r="D77" s="6" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="78" spans="3:4">
       <c r="C78" t="s">
         <v>164</v>
       </c>
-      <c r="D78">
-        <v>357</v>
+      <c r="D78" s="6" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="79" spans="3:4">
       <c r="C79" t="s">
         <v>165</v>
       </c>
-      <c r="D79">
-        <v>358</v>
+      <c r="D79" s="6" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="80" spans="3:4">
       <c r="C80" t="s">
         <v>166</v>
       </c>
-      <c r="D80">
-        <v>321</v>
+      <c r="D80" s="6" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="81" spans="3:4">
       <c r="C81" t="s">
         <v>167</v>
       </c>
-      <c r="D81">
-        <v>322</v>
+      <c r="D81" s="6" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="82" spans="3:4">
       <c r="C82" t="s">
         <v>168</v>
       </c>
-      <c r="D82">
-        <v>323</v>
+      <c r="D82" s="6" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="83" spans="3:4">
       <c r="C83" t="s">
         <v>169</v>
       </c>
-      <c r="D83">
-        <v>324</v>
+      <c r="D83" s="6" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="84" spans="3:4">
       <c r="C84" t="s">
         <v>170</v>
       </c>
-      <c r="D84">
-        <v>325</v>
+      <c r="D84" s="6" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="85" spans="3:4">
       <c r="C85" t="s">
         <v>171</v>
       </c>
-      <c r="D85">
-        <v>326</v>
+      <c r="D85" s="6" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="86" spans="3:4">
       <c r="C86" t="s">
         <v>172</v>
       </c>
-      <c r="D86">
-        <v>327</v>
+      <c r="D86" s="6" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="87" spans="3:4">
       <c r="C87" t="s">
         <v>173</v>
       </c>
-      <c r="D87">
-        <v>316</v>
+      <c r="D87" s="6" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="88" spans="3:4">
       <c r="C88" t="s">
         <v>174</v>
       </c>
-      <c r="D88">
-        <v>317</v>
+      <c r="D88" s="6" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="89" spans="3:4">
       <c r="C89" t="s">
         <v>175</v>
       </c>
-      <c r="D89">
-        <v>318</v>
+      <c r="D89" s="6" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="90" spans="3:4">
       <c r="C90" t="s">
         <v>176</v>
       </c>
-      <c r="D90">
-        <v>319</v>
+      <c r="D90" s="6" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="91" spans="3:4">
       <c r="C91" t="s">
         <v>177</v>
       </c>
-      <c r="D91">
-        <v>320</v>
+      <c r="D91" s="6" t="s">
+        <v>292</v>
       </c>
     </row>
   </sheetData>

--- a/input_data.xlsx
+++ b/input_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/weigu/Documents/Exercise/qzz_autoType/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6443785-B437-E442-A136-0445CB90F1CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8104C2F-E433-5B40-A4DB-00D7267BD0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="20460" activeTab="2" xr2:uid="{8B1B3161-B270-384F-BA23-5AA6E4650D06}"/>
+    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="20460" xr2:uid="{8B1B3161-B270-384F-BA23-5AA6E4650D06}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="296">
   <si>
     <t>企业名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1013,6 +1013,13 @@
   </si>
   <si>
     <t>批发和零售业</t>
+  </si>
+  <si>
+    <t>交通运输、仓储和邮政业</t>
+  </si>
+  <si>
+    <t>莆田xxx熊公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1461,7 +1468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA2E47FE-C844-5240-8BE9-FEA7EB7E19A5}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="32.6640625" customWidth="1"/>
@@ -1622,6 +1629,49 @@
         <v>506638468441612312</v>
       </c>
     </row>
+    <row r="5" spans="1:13">
+      <c r="B5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <f>VLOOKUP(C4,sheet2!A:B,2,FALSE)</f>
+        <v>350000</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <f>VLOOKUP(E4,sheet2!C:D,2,FALSE)</f>
+        <v>350300</v>
+      </c>
+      <c r="G5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5">
+        <f>VLOOKUP(G5,sheet2!E:F,2,FALSE)</f>
+        <v>350322</v>
+      </c>
+      <c r="I5" t="s">
+        <v>202</v>
+      </c>
+      <c r="J5" t="s">
+        <v>294</v>
+      </c>
+      <c r="K5" s="5">
+        <f>VLOOKUP(J5,Sheet3!A:B,2,FALSE)</f>
+        <v>100089</v>
+      </c>
+      <c r="L5" t="s">
+        <v>100</v>
+      </c>
+      <c r="M5" s="5" t="str">
+        <f>VLOOKUP(L5,Sheet3!C:D,2,FALSE)</f>
+        <v>506638468433223684</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
@@ -1634,7 +1684,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J1048576" xr:uid="{EF5F83EB-8102-6549-BB35-721D92BBA3D8}">
       <formula1>行业_一级</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G1048576 L3:L1048576 E3:E1048576" xr:uid="{1B598FD6-123C-7E4F-8E23-947CF644E04E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G1048576 E3:E1048576 L3:L1048576" xr:uid="{1B598FD6-123C-7E4F-8E23-947CF644E04E}">
       <formula1>INDIRECT(C3)</formula1>
     </dataValidation>
   </dataValidations>

--- a/input_data.xlsx
+++ b/input_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/weigu/Documents/Exercise/qzz_autoType/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8104C2F-E433-5B40-A4DB-00D7267BD0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79994C35-E9D0-6243-967E-363DB8798F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="20460" xr2:uid="{8B1B3161-B270-384F-BA23-5AA6E4650D06}"/>
+    <workbookView xWindow="1360" yWindow="-19880" windowWidth="30220" windowHeight="20460" xr2:uid="{8B1B3161-B270-384F-BA23-5AA6E4650D06}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="305">
   <si>
     <t>企业名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -734,14 +734,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>莆田市鑫龙鞋业有限公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tCMtsj5+SRbxdub540itVw==</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>506638468429029376</t>
   </si>
   <si>
@@ -1012,13 +1004,48 @@
     <t>506638468445806617</t>
   </si>
   <si>
-    <t>批发和零售业</t>
-  </si>
-  <si>
-    <t>交通运输、仓储和邮政业</t>
-  </si>
-  <si>
-    <t>莆田xxx熊公司</t>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Location_encrypt</t>
+  </si>
+  <si>
+    <t>address_encrpt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>南京南瑞继保电气有限公司</t>
+  </si>
+  <si>
+    <t>江苏省</t>
+  </si>
+  <si>
+    <t>南京市</t>
+  </si>
+  <si>
+    <t>江苏省/南京市/江宁区</t>
+  </si>
+  <si>
+    <t>南京江宁经济技术开发区苏源大道69号</t>
+  </si>
+  <si>
+    <t>南京国电南自电网自动化有限公司</t>
+  </si>
+  <si>
+    <t>南京市江宁经济技术开发区水阁路39号</t>
+  </si>
+  <si>
+    <t>制造业</t>
+  </si>
+  <si>
+    <t>IVzBHJkOm4lwj/RpURxxo7M9EczDS8thaV4frJgqBlY=</t>
+  </si>
+  <si>
+    <t>c/Fw4F9PV43mhS3F6SDdjHmsed0Rkr5Ue2OBHrkEfsIhjlWI0w8y26rWWOGuABgZFRk330emT7FMXqebuDjvHw==</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LULDW/qcY8qiC/i5cc7xLaE9xvrrNZBtg22CWgOstlMUSdePR9AMad8Xc8FYZW3uFRk330emT7FMXqebuDjvHw==</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1029,7 +1056,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1062,8 +1089,23 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="SimSun"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1076,8 +1118,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED973"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1100,13 +1148,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1133,6 +1196,33 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1468,18 +1558,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA2E47FE-C844-5240-8BE9-FEA7EB7E19A5}">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="32.6640625" customWidth="1"/>
     <col min="3" max="4" width="13.33203125" customWidth="1"/>
-    <col min="9" max="9" width="45.1640625" customWidth="1"/>
-    <col min="10" max="10" width="34.1640625" customWidth="1"/>
-    <col min="11" max="11" width="17.1640625" customWidth="1"/>
-    <col min="12" max="12" width="21.6640625" customWidth="1"/>
+    <col min="9" max="9" width="33.83203125" customWidth="1"/>
+    <col min="10" max="10" width="41.6640625" customWidth="1"/>
+    <col min="11" max="12" width="45.1640625" customWidth="1"/>
+    <col min="13" max="13" width="44.5" customWidth="1"/>
+    <col min="14" max="14" width="17.1640625" customWidth="1"/>
+    <col min="15" max="15" width="43.1640625" customWidth="1"/>
+    <col min="16" max="16" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="67" customHeight="1">
+    <row r="1" spans="1:29" ht="67" customHeight="1">
       <c r="A1" s="7" t="s">
         <v>200</v>
       </c>
@@ -1495,8 +1588,11 @@
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
       <c r="M1" s="8"/>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+    </row>
+    <row r="2" spans="1:29" ht="17">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1521,23 +1617,32 @@
       <c r="H2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="L2" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:29" ht="17">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -1565,126 +1670,171 @@
         <f>VLOOKUP(G3,sheet2!E:F,2,FALSE)</f>
         <v>350322</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="12" t="str">
+        <f>C3&amp;"/"&amp;E3&amp;"/"&amp;G3</f>
+        <v>福建省/莆田市/仙游县</v>
+      </c>
+      <c r="J3" s="11"/>
+      <c r="K3" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="L3" s="5"/>
+      <c r="M3" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="K3" s="5">
-        <f>VLOOKUP(J3,Sheet3!A:B,2,FALSE)</f>
+      <c r="N3" s="5">
+        <f>VLOOKUP(M3,Sheet3!A:B,2,FALSE)</f>
         <v>100086</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="M3" s="5" t="str">
-        <f>VLOOKUP(L3,Sheet3!C:D,2,FALSE)</f>
+      <c r="P3" s="5" t="str">
+        <f>VLOOKUP(O3,Sheet3!C:D,2,FALSE)</f>
         <v>506638468429029376</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4">
+    <row r="4" spans="1:29" ht="36" customHeight="1">
+      <c r="A4" s="13">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4">
-        <f>VLOOKUP(C3,sheet2!A:B,2,FALSE)</f>
-        <v>350000</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4">
-        <f>VLOOKUP(E3,sheet2!C:D,2,FALSE)</f>
-        <v>350300</v>
-      </c>
-      <c r="G4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H4">
-        <f>VLOOKUP(G4,sheet2!E:F,2,FALSE)</f>
-        <v>350304</v>
-      </c>
-      <c r="I4" t="s">
-        <v>202</v>
-      </c>
-      <c r="J4" t="s">
-        <v>293</v>
-      </c>
-      <c r="K4" s="5">
-        <f>VLOOKUP(J4,Sheet3!A:B,2,FALSE)</f>
-        <v>100088</v>
-      </c>
-      <c r="L4" t="s">
-        <v>140</v>
-      </c>
-      <c r="M4" s="5" t="str">
-        <f>VLOOKUP(L4,Sheet3!C:D,2,FALSE)</f>
-        <v>506638468441612312</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="B5" t="s">
+      <c r="B4" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <f>VLOOKUP(C4,sheet2!A:B,2,FALSE)</f>
-        <v>350000</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5">
-        <f>VLOOKUP(E4,sheet2!C:D,2,FALSE)</f>
-        <v>350300</v>
-      </c>
-      <c r="G5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5">
-        <f>VLOOKUP(G5,sheet2!E:F,2,FALSE)</f>
-        <v>350322</v>
-      </c>
-      <c r="I5" t="s">
-        <v>202</v>
-      </c>
-      <c r="J5" t="s">
-        <v>294</v>
-      </c>
-      <c r="K5" s="5">
-        <f>VLOOKUP(J5,Sheet3!A:B,2,FALSE)</f>
-        <v>100089</v>
-      </c>
-      <c r="L5" t="s">
-        <v>100</v>
-      </c>
-      <c r="M5" s="5" t="str">
-        <f>VLOOKUP(L5,Sheet3!C:D,2,FALSE)</f>
-        <v>506638468433223684</v>
-      </c>
+      <c r="D4" s="13">
+        <v>320000</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="F4" s="13">
+        <v>320100</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="13">
+        <v>320115</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="M4" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="N4" s="13">
+        <v>100086</v>
+      </c>
+      <c r="O4" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="P4" s="17" t="str">
+        <f>VLOOKUP(O4,Sheet3!C:D,2,FALSE)</f>
+        <v>506638468429029377</v>
+      </c>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="16"/>
+      <c r="V4" s="16"/>
+      <c r="W4" s="16"/>
+      <c r="X4" s="16"/>
+      <c r="Y4" s="16"/>
+      <c r="Z4" s="16"/>
+      <c r="AA4" s="16"/>
+      <c r="AB4" s="16"/>
+      <c r="AC4" s="16"/>
+    </row>
+    <row r="5" spans="1:29" ht="54">
+      <c r="A5" s="13">
+        <v>3</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="D5" s="13">
+        <v>320000</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="F5" s="13">
+        <v>320100</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="13">
+        <v>320115</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="N5" s="13">
+        <v>100101</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="P5" s="17" t="str">
+        <f>VLOOKUP(O5,Sheet3!C:D,2,FALSE)</f>
+        <v>506638468445806600</v>
+      </c>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="16"/>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="16"/>
+      <c r="AA5" s="16"/>
+      <c r="AB5" s="16"/>
+      <c r="AC5" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:P1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C1048576" xr:uid="{107AFD8A-FE7D-E141-B82C-3FDF47235C83}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3 C6:C1048576" xr:uid="{107AFD8A-FE7D-E141-B82C-3FDF47235C83}">
       <formula1>省</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J1048576" xr:uid="{EF5F83EB-8102-6549-BB35-721D92BBA3D8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 M6:M1048576" xr:uid="{EF5F83EB-8102-6549-BB35-721D92BBA3D8}">
       <formula1>行业_一级</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G1048576 E3:E1048576 L3:L1048576" xr:uid="{1B598FD6-123C-7E4F-8E23-947CF644E04E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:E1048576 O6:O1048576 O3 E3 G3 G6:G1048576" xr:uid="{1B598FD6-123C-7E4F-8E23-947CF644E04E}">
       <formula1>INDIRECT(C3)</formula1>
     </dataValidation>
   </dataValidations>
@@ -2259,7 +2409,7 @@
         <v>90</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2273,7 +2423,7 @@
         <v>91</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2287,7 +2437,7 @@
         <v>92</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2301,7 +2451,7 @@
         <v>93</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2315,7 +2465,7 @@
         <v>94</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2329,7 +2479,7 @@
         <v>95</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2343,7 +2493,7 @@
         <v>96</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2357,7 +2507,7 @@
         <v>97</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2371,7 +2521,7 @@
         <v>98</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2385,7 +2535,7 @@
         <v>99</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2399,7 +2549,7 @@
         <v>100</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2413,7 +2563,7 @@
         <v>101</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2427,7 +2577,7 @@
         <v>102</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2441,7 +2591,7 @@
         <v>103</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2455,7 +2605,7 @@
         <v>104</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2469,7 +2619,7 @@
         <v>105</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2483,7 +2633,7 @@
         <v>106</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2497,7 +2647,7 @@
         <v>107</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2505,7 +2655,7 @@
         <v>108</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2513,7 +2663,7 @@
         <v>109</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2521,7 +2671,7 @@
         <v>110</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2529,7 +2679,7 @@
         <v>111</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2537,7 +2687,7 @@
         <v>112</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2545,7 +2695,7 @@
         <v>113</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2553,7 +2703,7 @@
         <v>114</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2561,7 +2711,7 @@
         <v>115</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2569,7 +2719,7 @@
         <v>88</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2577,7 +2727,7 @@
         <v>116</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2585,7 +2735,7 @@
         <v>117</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2593,7 +2743,7 @@
         <v>118</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2601,7 +2751,7 @@
         <v>119</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="33" spans="3:4">
@@ -2609,7 +2759,7 @@
         <v>120</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" spans="3:4">
@@ -2617,7 +2767,7 @@
         <v>121</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="35" spans="3:4">
@@ -2625,7 +2775,7 @@
         <v>122</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="36" spans="3:4">
@@ -2633,7 +2783,7 @@
         <v>123</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="37" spans="3:4">
@@ -2641,7 +2791,7 @@
         <v>124</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="38" spans="3:4">
@@ -2649,7 +2799,7 @@
         <v>125</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="39" spans="3:4">
@@ -2657,7 +2807,7 @@
         <v>126</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="40" spans="3:4">
@@ -2665,7 +2815,7 @@
         <v>127</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="41" spans="3:4">
@@ -2673,7 +2823,7 @@
         <v>128</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="42" spans="3:4">
@@ -2681,7 +2831,7 @@
         <v>129</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="43" spans="3:4">
@@ -2689,7 +2839,7 @@
         <v>130</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="44" spans="3:4">
@@ -2697,7 +2847,7 @@
         <v>131</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="45" spans="3:4">
@@ -2705,7 +2855,7 @@
         <v>132</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46" spans="3:4">
@@ -2713,7 +2863,7 @@
         <v>133</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="47" spans="3:4">
@@ -2721,7 +2871,7 @@
         <v>134</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="48" spans="3:4">
@@ -2729,7 +2879,7 @@
         <v>89</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="49" spans="3:4">
@@ -2737,7 +2887,7 @@
         <v>135</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="50" spans="3:4">
@@ -2745,7 +2895,7 @@
         <v>136</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="51" spans="3:4">
@@ -2753,7 +2903,7 @@
         <v>137</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="52" spans="3:4">
@@ -2761,7 +2911,7 @@
         <v>138</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="53" spans="3:4">
@@ -2769,7 +2919,7 @@
         <v>139</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="54" spans="3:4">
@@ -2777,7 +2927,7 @@
         <v>140</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="55" spans="3:4">
@@ -2785,7 +2935,7 @@
         <v>141</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="56" spans="3:4">
@@ -2793,7 +2943,7 @@
         <v>142</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="57" spans="3:4">
@@ -2801,7 +2951,7 @@
         <v>143</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="58" spans="3:4">
@@ -2809,7 +2959,7 @@
         <v>144</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="59" spans="3:4">
@@ -2817,7 +2967,7 @@
         <v>145</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="60" spans="3:4">
@@ -2825,7 +2975,7 @@
         <v>146</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="61" spans="3:4">
@@ -2833,7 +2983,7 @@
         <v>147</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="62" spans="3:4">
@@ -2841,7 +2991,7 @@
         <v>148</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="63" spans="3:4">
@@ -2849,7 +2999,7 @@
         <v>149</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="64" spans="3:4">
@@ -2857,7 +3007,7 @@
         <v>150</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="65" spans="3:4">
@@ -2865,7 +3015,7 @@
         <v>151</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="66" spans="3:4">
@@ -2873,7 +3023,7 @@
         <v>152</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="67" spans="3:4">
@@ -2881,7 +3031,7 @@
         <v>153</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="68" spans="3:4">
@@ -2889,7 +3039,7 @@
         <v>154</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="69" spans="3:4">
@@ -2897,7 +3047,7 @@
         <v>155</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="70" spans="3:4">
@@ -2905,7 +3055,7 @@
         <v>156</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="71" spans="3:4">
@@ -2913,7 +3063,7 @@
         <v>157</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="72" spans="3:4">
@@ -2921,7 +3071,7 @@
         <v>158</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="73" spans="3:4">
@@ -2929,7 +3079,7 @@
         <v>159</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="74" spans="3:4">
@@ -2937,7 +3087,7 @@
         <v>160</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="75" spans="3:4">
@@ -2945,7 +3095,7 @@
         <v>161</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="76" spans="3:4">
@@ -2953,7 +3103,7 @@
         <v>162</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="77" spans="3:4">
@@ -2961,7 +3111,7 @@
         <v>163</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="78" spans="3:4">
@@ -2969,7 +3119,7 @@
         <v>164</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="79" spans="3:4">
@@ -2977,7 +3127,7 @@
         <v>165</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="80" spans="3:4">
@@ -2985,7 +3135,7 @@
         <v>166</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="81" spans="3:4">
@@ -2993,7 +3143,7 @@
         <v>167</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="82" spans="3:4">
@@ -3001,7 +3151,7 @@
         <v>168</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="83" spans="3:4">
@@ -3009,7 +3159,7 @@
         <v>169</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="84" spans="3:4">
@@ -3017,7 +3167,7 @@
         <v>170</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="85" spans="3:4">
@@ -3025,7 +3175,7 @@
         <v>171</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="86" spans="3:4">
@@ -3033,7 +3183,7 @@
         <v>172</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="87" spans="3:4">
@@ -3041,7 +3191,7 @@
         <v>173</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="88" spans="3:4">
@@ -3049,7 +3199,7 @@
         <v>174</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="89" spans="3:4">
@@ -3057,7 +3207,7 @@
         <v>175</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="90" spans="3:4">
@@ -3065,7 +3215,7 @@
         <v>176</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="91" spans="3:4">
@@ -3073,7 +3223,7 @@
         <v>177</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
